--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F484"/>
+  <dimension ref="A1:F487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12042,6 +12042,78 @@
       <c r="F484" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>295.79</v>
+      </c>
+      <c r="C485" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="D485" t="n">
+        <v>186.73</v>
+      </c>
+      <c r="E485" t="n">
+        <v>215.11</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>280.68</v>
+      </c>
+      <c r="C486" t="n">
+        <v>178.46</v>
+      </c>
+      <c r="D486" t="n">
+        <v>187.54</v>
+      </c>
+      <c r="E486" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="C487" t="n">
+        <v>178.46</v>
+      </c>
+      <c r="D487" t="n">
+        <v>190.69</v>
+      </c>
+      <c r="E487" t="n">
+        <v>220.25</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17319,6 +17391,36 @@
       </c>
       <c r="B526" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -17481,28 +17583,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9567264971254202</v>
+        <v>0.9264344836380534</v>
       </c>
       <c r="J2" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K2" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05045603887962591</v>
+        <v>0.04786678679857959</v>
       </c>
       <c r="M2" t="n">
-        <v>18.39344213041025</v>
+        <v>18.52053944744432</v>
       </c>
       <c r="N2" t="n">
-        <v>1035.882187473358</v>
+        <v>1034.267666817302</v>
       </c>
       <c r="O2" t="n">
-        <v>32.18512369827648</v>
+        <v>32.16003213333752</v>
       </c>
       <c r="P2" t="n">
-        <v>281.7875131322216</v>
+        <v>282.0982359464114</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17553,28 +17655,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2797228168788345</v>
+        <v>0.2776161893291997</v>
       </c>
       <c r="J3" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K3" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09324134163291564</v>
+        <v>0.09307101500593251</v>
       </c>
       <c r="M3" t="n">
-        <v>4.516999310978342</v>
+        <v>4.49827791278927</v>
       </c>
       <c r="N3" t="n">
-        <v>45.777029399386</v>
+        <v>45.51614086362541</v>
       </c>
       <c r="O3" t="n">
-        <v>6.765872404899903</v>
+        <v>6.746565115940512</v>
       </c>
       <c r="P3" t="n">
-        <v>173.208839743604</v>
+        <v>173.2304372119256</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17625,28 +17727,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2250638050875619</v>
+        <v>0.2271456111995483</v>
       </c>
       <c r="J4" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.101212115866535</v>
+        <v>0.1040347064525279</v>
       </c>
       <c r="M4" t="n">
-        <v>4.13373171961933</v>
+        <v>4.12161738179402</v>
       </c>
       <c r="N4" t="n">
-        <v>27.0115767488902</v>
+        <v>26.8815199426178</v>
       </c>
       <c r="O4" t="n">
-        <v>5.197266276504427</v>
+        <v>5.184739139302748</v>
       </c>
       <c r="P4" t="n">
-        <v>180.4711796211397</v>
+        <v>180.4498082320444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17697,28 +17799,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09018510025361533</v>
+        <v>0.08755166551752487</v>
       </c>
       <c r="J5" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K5" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002554350025688712</v>
+        <v>0.002439758322868468</v>
       </c>
       <c r="M5" t="n">
-        <v>10.660538514935</v>
+        <v>10.60714952819449</v>
       </c>
       <c r="N5" t="n">
-        <v>191.8921855848371</v>
+        <v>190.769210055311</v>
       </c>
       <c r="O5" t="n">
-        <v>13.8525154966467</v>
+        <v>13.81192275012103</v>
       </c>
       <c r="P5" t="n">
-        <v>218.0419529507325</v>
+        <v>218.0688147598402</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17756,7 +17858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F484"/>
+  <dimension ref="A1:F487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33227,6 +33329,102 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-46.89042727232765,168.13430945399867</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-46.890577936923286,168.13247813225087</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-46.89124201553725,168.1320675842961</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-46.89199670661874,168.131907777475</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-46.89036397595105,168.13413428884982</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-46.890571569319285,168.13246051157438</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-46.89124540883576,168.13207697434797</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-46.89201417590395,168.13195611946978</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-46.89031462889753,168.13399772756873</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-46.890571569319285,168.13246051157438</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-46.89125860498965,168.132113491228</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-46.89201823949988,168.1319673644948</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F487"/>
+  <dimension ref="A1:F489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>295.79</v>
+        <v>309.34</v>
       </c>
       <c r="C485" t="n">
         <v>179.98</v>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>280.68</v>
+        <v>309.34</v>
       </c>
       <c r="C486" t="n">
         <v>178.46</v>
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>268.9</v>
+        <v>309.34</v>
       </c>
       <c r="C487" t="n">
         <v>178.46</v>
@@ -12114,6 +12114,54 @@
       <c r="F487" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>308.91</v>
+      </c>
+      <c r="C488" t="n">
+        <v>179.42</v>
+      </c>
+      <c r="D488" t="n">
+        <v>190.65</v>
+      </c>
+      <c r="E488" t="n">
+        <v>219.62</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="C489" t="n">
+        <v>178.34</v>
+      </c>
+      <c r="D489" t="n">
+        <v>191.51</v>
+      </c>
+      <c r="E489" t="n">
+        <v>220</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17421,6 +17469,26 @@
       </c>
       <c r="B529" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17583,28 +17651,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9264344836380534</v>
+        <v>0.9597986076747209</v>
       </c>
       <c r="J2" t="n">
+        <v>488</v>
+      </c>
+      <c r="K2" t="n">
         <v>486</v>
       </c>
-      <c r="K2" t="n">
-        <v>484</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04786678679857959</v>
+        <v>0.05186159752138342</v>
       </c>
       <c r="M2" t="n">
-        <v>18.52053944744432</v>
+        <v>18.21218321996985</v>
       </c>
       <c r="N2" t="n">
-        <v>1034.267666817302</v>
+        <v>1025.250508639603</v>
       </c>
       <c r="O2" t="n">
-        <v>32.16003213333752</v>
+        <v>32.01953323581721</v>
       </c>
       <c r="P2" t="n">
-        <v>282.0982359464114</v>
+        <v>281.755982336987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17655,28 +17723,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2776161893291997</v>
+        <v>0.2761706014779456</v>
       </c>
       <c r="J3" t="n">
+        <v>488</v>
+      </c>
+      <c r="K3" t="n">
         <v>486</v>
       </c>
-      <c r="K3" t="n">
-        <v>484</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.09307101500593251</v>
+        <v>0.0929183390193089</v>
       </c>
       <c r="M3" t="n">
-        <v>4.49827791278927</v>
+        <v>4.486090644283014</v>
       </c>
       <c r="N3" t="n">
-        <v>45.51614086362541</v>
+        <v>45.3441677409293</v>
       </c>
       <c r="O3" t="n">
-        <v>6.746565115940512</v>
+        <v>6.7338078188295</v>
       </c>
       <c r="P3" t="n">
-        <v>173.2304372119256</v>
+        <v>173.245296568461</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17727,28 +17795,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2271456111995483</v>
+        <v>0.2306227176432052</v>
       </c>
       <c r="J4" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K4" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1040347064525279</v>
+        <v>0.1074664863439504</v>
       </c>
       <c r="M4" t="n">
-        <v>4.12161738179402</v>
+        <v>4.127045025091144</v>
       </c>
       <c r="N4" t="n">
-        <v>26.8815199426178</v>
+        <v>26.85337900767881</v>
       </c>
       <c r="O4" t="n">
-        <v>5.184739139302748</v>
+        <v>5.182024605082344</v>
       </c>
       <c r="P4" t="n">
-        <v>180.4498082320444</v>
+        <v>180.4140478260886</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17799,28 +17867,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08755166551752487</v>
+        <v>0.087069880667532</v>
       </c>
       <c r="J5" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002439758322868468</v>
+        <v>0.002434671164315727</v>
       </c>
       <c r="M5" t="n">
-        <v>10.60714952819449</v>
+        <v>10.56594079148404</v>
       </c>
       <c r="N5" t="n">
-        <v>190.769210055311</v>
+        <v>189.9890918677046</v>
       </c>
       <c r="O5" t="n">
-        <v>13.81192275012103</v>
+        <v>13.78365306686528</v>
       </c>
       <c r="P5" t="n">
-        <v>218.0688147598402</v>
+        <v>218.0737448593689</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17858,7 +17926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F487"/>
+  <dimension ref="A1:F489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33337,7 +33405,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>-46.89042727232765,168.13430945399867</t>
+          <t>-46.89048403358766,168.13446653495689</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -33369,7 +33437,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>-46.89036397595105,168.13413428884982</t>
+          <t>-46.89048403358766,168.13446653495689</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -33401,7 +33469,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>-46.89031462889753,168.13399772756873</t>
+          <t>-46.89048403358766,168.13446653495689</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -33422,6 +33490,70 @@
       <c r="F487" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.89048223231096,168.13446155009458</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.89057559096422,168.13247164042218</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.89125843741953,168.13211302752146</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.89201560025728,168.13196006102473</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.89048353090581,168.1344651438325</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.89057106661359,168.13245912046852</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.89126204017713,168.13212299721255</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.89201719218144,168.13196446629232</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0588/nzd0588.xlsx
+++ b/data/nzd0588/nzd0588.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:F491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12162,6 +12162,54 @@
       <c r="F489" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>308.44</v>
+      </c>
+      <c r="C490" t="n">
+        <v>177.84</v>
+      </c>
+      <c r="D490" t="n">
+        <v>193.71</v>
+      </c>
+      <c r="E490" t="n">
+        <v>221.24</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="C491" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="D491" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="E491" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17489,6 +17537,26 @@
       </c>
       <c r="B531" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -17651,28 +17719,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9597986076747209</v>
+        <v>0.9597353218496677</v>
       </c>
       <c r="J2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K2" t="n">
         <v>488</v>
       </c>
-      <c r="K2" t="n">
-        <v>486</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.05186159752138342</v>
+        <v>0.05229945862226648</v>
       </c>
       <c r="M2" t="n">
-        <v>18.21218321996985</v>
+        <v>18.14056636683604</v>
       </c>
       <c r="N2" t="n">
-        <v>1025.250508639603</v>
+        <v>1021.050680759606</v>
       </c>
       <c r="O2" t="n">
-        <v>32.01953323581721</v>
+        <v>31.95388365691417</v>
       </c>
       <c r="P2" t="n">
-        <v>281.755982336987</v>
+        <v>281.7566423116744</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17723,28 +17791,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2761706014779456</v>
+        <v>0.2740678444234387</v>
       </c>
       <c r="J3" t="n">
+        <v>490</v>
+      </c>
+      <c r="K3" t="n">
         <v>488</v>
       </c>
-      <c r="K3" t="n">
-        <v>486</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0929183390193089</v>
+        <v>0.09233448032579306</v>
       </c>
       <c r="M3" t="n">
-        <v>4.486090644283014</v>
+        <v>4.476753332228204</v>
       </c>
       <c r="N3" t="n">
-        <v>45.3441677409293</v>
+        <v>45.18839265089963</v>
       </c>
       <c r="O3" t="n">
-        <v>6.7338078188295</v>
+        <v>6.722231225634807</v>
       </c>
       <c r="P3" t="n">
-        <v>173.245296568461</v>
+        <v>173.2670237205096</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17795,28 +17863,28 @@
         <v>0.1402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2306227176432052</v>
+        <v>0.2357675196699672</v>
       </c>
       <c r="J4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1074664863439504</v>
+        <v>0.112004449740377</v>
       </c>
       <c r="M4" t="n">
-        <v>4.127045025091144</v>
+        <v>4.142849223910483</v>
       </c>
       <c r="N4" t="n">
-        <v>26.85337900767881</v>
+        <v>26.92281513052756</v>
       </c>
       <c r="O4" t="n">
-        <v>5.182024605082344</v>
+        <v>5.188719989605101</v>
       </c>
       <c r="P4" t="n">
-        <v>180.4140478260886</v>
+        <v>180.3608553574991</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17867,28 +17935,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.087069880667532</v>
+        <v>0.08690930051143085</v>
       </c>
       <c r="J5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002434671164315727</v>
+        <v>0.002447511144463066</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56594079148404</v>
+        <v>10.52684587061373</v>
       </c>
       <c r="N5" t="n">
-        <v>189.9890918677046</v>
+        <v>189.2179765820968</v>
       </c>
       <c r="O5" t="n">
-        <v>13.78365306686528</v>
+        <v>13.75565253203558</v>
       </c>
       <c r="P5" t="n">
-        <v>218.0737448593689</v>
+        <v>218.0754055524106</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17926,7 +17994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:F491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33557,6 +33625,70 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.89048026347339,168.13445610152462</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.89056897200639,168.13245332419442</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.89127125653002,168.1321485010797</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.89202238688024,168.1319788413779</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.89047460830032,168.13444045137905</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.89057056390789,168.13245772936267</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.891268114592144,168.1321398065785</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.892013924547456,168.13195542390127</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
